--- a/translations/welsh-translations/december-waste/xlsx/07-obligations-home-no-obligations.xlsx
+++ b/translations/welsh-translations/december-waste/xlsx/07-obligations-home-no-obligations.xlsx
@@ -163,7 +163,7 @@
     <t>Download a list of all PRNs and PERNs for {0} (CSV)</t>
   </si>
   <si>
-    <t>Lawrlwytho rhestr o'r holl PRNs a PERNs ar gyfer {0} ar gyfer {0</t>
+    <t>Lawrlwytho rhestr o'r holl PRNs a PERNs ar gyfer {0} (CSV)</t>
   </si>
   <si>
     <t>src/FrontendSchemeRegistration.UI/Resources/Views/Shared/Partials/Prns/_obligationsHeader.en.resx::compliance_scheme</t>
